--- a/pensum/ol12/OL12_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol12/OL12_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="152">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 12: Organisasjonens interne rammebetingelser (V5)</t>
   </si>
@@ -170,12 +170,36 @@
     <t xml:space="preserve">c)  Kontoret bruker 6 timer i uka på å taste inn timelistene på nytt, i 46 arbeidsuker. Hvor mange timer i året er det?</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timer i året = timer per uke × antall arbeidsuker. Begrunnelsen for å regne på det står i 12.1: bare aktiviteter som bidrar til måloppnåelse, bør utføres.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Kari sier: «Tom har tjue års erfaring. Da trenger han ikke nytt kurs på gjeldende norm.» Hva er riktig etter læreboka?   A: Riktig: lang erfaring teller som formell kompetanse   B: Feil: erfaringen er realkompetanse, og kompetansen er ikke konstant; den skal utvikles hele tiden   C: Riktig: kursbevis er bare papir og betyr lite for oppdragene   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Karis plan om digital timeregistrering er en endring i teknologihjørnet. Bruk Leavitts diamant: hvilke av de tre andre hjørnene må flytte seg for at planen skal virke? Tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Leavitts diamant (figur 12.1) og bokas tre spørsmål om teknologi (12.3). At endringer i det tekniske ikke bør innføres uten samtidige tilpasninger i det sosiale, er lærdommen fra Tavistock-forskningen (15.5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formell eller real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør: kan personen legge fram et papir på det? Fagbrev, kursbevis og vitnemål er formell kompetanse. Erfaring uten papir er realkompetanse. Hvordan en person er, er en personlig egenskap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hjørnet og timene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teknologi er også de administrative rutinene som støtter produksjonen (12.3). Timene: timer i uka ganger antall arbeidsuker.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 12, figur 12.1 (Leavitts diamant), avsnitt 12.1 (mål), 12.2 (deltagere og kompetanse) og 12.3 (teknologi, tabell 12.1). Fakta om folkene og timelistene er de samme som i appen kap. 12. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -260,12 +284,30 @@
     <t xml:space="preserve">c)  Montørene henter materiell fire ganger i uka, 45 minutter per tur, i 46 arbeidsuker. Hvor mange timer i året er det?</t>
   </si>
   <si>
+    <t xml:space="preserve">Timer i året = turer per uke × timer per tur × arbeidsuker. Begrunnelsen står i 12.1: bare aktiviteter som bidrar til måloppnåelse, bør utføres.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona sier: «Vi er tre elektrikere. Teknologi har vi nesten ikke.» Hva er riktig etter læreboka?   A: Riktig: teknologi er datamaskiner og automatisering   B: Feil: teknologi er verktøy og metoder i produksjonen, og de administrative rutinene som støtter den   C: Riktig: små bedrifter har ingen teknologi før de kjøper programvare   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Bør Mona ta i bruk KI-verktøyet? Bruk lærebokas tre spørsmål om teknologi (kvalitet, kostnad, trygghet), og si hvor grensen går for hva verktøyet kan gjøre. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Bokas tre spørsmål om teknologi: konkurransedyktig kvalitet, kostnadseffektiv, trygg for mennesker og miljø (Organisasjon og ledelse 12.3). Om KI: svar formulert som om en fagperson har skrevet dem, men generert av maskin- og programvare (12.3.1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internt eller eksternt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør: er dette et forhold inne i Fjell, noe bedriften selv har eller gjør? Kompetanse, utstyr og økonomi er internt. Arbeidsmarkedet, konkurrentene og renten er eksternt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Målet og timene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Et forretningsforetak styrer etter økonomiske mål (12.1). Timene: turer i uka × 0,75 time × 46 uker.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 12, innledningen (interne arbeidsbetingelser), avsnitt 12.1 (mål), 12.3 og 12.3.1 (teknologi og kunstig intelligens) og 12.5.2 (økonomi). Materiellhentingen er fra MA08. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -323,6 +365,9 @@
     <t xml:space="preserve">a)  Hva er Karis kontrollspenn, altså hvor mange personer har hun direkte under seg?</t>
   </si>
   <si>
+    <t xml:space="preserve">Kontrollspenn = antall underordnede én leder har direkte under seg. Fayol: kontrollspennet må være begrenset; seks til ti underordnede anses optimalt (Organisasjon og ledelse 14.2).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Ida regner anbud og priser for alle avdelingene, men gir ikke ordre til montørene. Hvor hører hun hjemme i organisasjonskartet?   A: I linjen, som avdelingsleder på nivå med Tom og Ronny   B: I staben: støtte for ledelsen, utenfor linjen, uten ordregivende myndighet   C: I den operative kjernen, sammen med montørene   (skriv bokstaven)</t>
   </si>
   <si>
@@ -335,6 +380,21 @@
     <t xml:space="preserve">e)  Hvilken endring i organisasjonskartet anbefaler du Kari, og hva bør skrives ned? Bruk begrepene kontrollspenn, enhetlig ledelse og formalisering. Tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Enhetlig ledelse, kontrollspenn og balanse mellom sentralisering og desentralisering (Fayol, Organisasjon og ledelse 14.2). Formalisering: hvem gjør hva når, hvem har myndighet over hvem, hvem rapporterer til hvem; stillingsinstrukser beskriver arbeidsoppgavene (15.6.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tell i kartet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kontrollspennet er alle som har lederen som nærmeste sjef. Hos Kari: kalkulatøren, de to avdelingslederne og montørene som ikke har noen leder mellom seg og henne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stab og inndeling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stab: støtte for ledelsen, utenfor linjen, uten ordregivende myndighet (14.4). Er avdelingene delt etter arbeidsoppgave, etter tjenestene eller etter kundene?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 12.4 (sosial struktur: organisasjonskart, over- og underordning, stillingsinstrukser), kap. 14.2 (Fayol: enhetlig ledelse, kontrollspenn, sentralisering), 14.4 (linje og stab) og 14.5–14.7 (funksjons-, produkt- og markedsdelt), kap. 15.6.2 (formalisering). Organisasjonskartet er det samme som i appen kap. 11. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -389,13 +449,34 @@
     <t xml:space="preserve">b)  Haugerud-jobben er 900 fakturerbare timer over seks måneder. Hvor mange timer i måneden er det?</t>
   </si>
   <si>
+    <t xml:space="preserve">Timer per måned = timer i alt / antall måneder. Et prosjekt skal løses innenfor en bestemt tidsramme (Organisasjon og ledelse 15.8.5).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Fjell har 3 500 fakturerbare timer i året. Hvor stor andel av timene i halvåret går til Haugerud-jobben, i prosent med én desimal?</t>
   </si>
   <si>
+    <t xml:space="preserve">Andel i prosent = del / helhet × 100. Helheten må gjelde samme periode som delen, her et halvår.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Mona sier: «Vi er bare tre. Vi trenger ikke skrive ned hvem som bestemmer hva på Haugerud.» Hva er riktig etter læreboka?   A: Riktig: formalisering trengs bare i store organisasjoner   B: Feil: et prosjekt har klart mål og tids- og kostnadsramme, og i en enkel struktur gir lite formalisering lett uklare ansvars- og myndighetsforhold   C: Riktig: prosjektet legges uansett ned når jobben er ferdig   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Tegn Fjell Elektro slik bedriften blir i halvåret med Haugerud-jobben. Hvem bestemmer hva på Haugerud, og hva er den største risikoen? To–tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosjektorganisasjon med kontrollerende autoritet: det overordnede administrative ansvaret ligger i basisorganisasjonen (Organisasjon og ledelse 15.8.5, figur 15.8). Utestående = måneder med kreditt × timer per måned × timepris. Økonomien som intern arbeidsbetingelse (12.5.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organisasjonstypen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Få ansatte, ingen fast arbeidsdeling, lite skrevet ned, og bare toppledelse og operativ kjerne: se 15.8.1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">900 timer delt på 6 måneder. Fjells timer i et halvår: 3 500 / 2 = 1 750. Andel = 900 / 1 750 × 100.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 15.8.1 (entreprenørorganisasjonen), 15.6.2 (formalisering) og 15.8.5 (prosjektoppgavens kjennetegn, prosjektorganisasjon med kontrollerende autoritet), kap. 12.4 (formelle trekk) og 12.5.2 (økonomi). Haugerud-jobben er fra MA05 og MA08. Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -409,7 +490,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -476,8 +557,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -494,6 +597,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFFBF6EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -546,7 +667,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -599,7 +720,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -632,8 +773,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -661,7 +802,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -964,7 +1105,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1219,80 +1360,143 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="11" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="B","Riktig","Prøv igjen"))</f>
+      <c r="B24" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+    </row>
+    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="11" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
+    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-    </row>
-    <row r="30" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="18"/>
+    </row>
+    <row r="38" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="28">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1311,11 +1515,16 @@
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A22:E22"/>
     <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
-    <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:G28"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A39:G39"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1332,7 +1541,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1343,7 +1552,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1353,7 +1562,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1364,7 +1573,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1388,10 +1597,10 @@
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1401,10 +1610,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1414,10 +1623,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1427,10 +1636,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1440,10 +1649,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1453,10 +1662,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1466,10 +1675,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1494,7 +1703,7 @@
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1503,7 +1712,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -1517,7 +1726,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1531,7 +1740,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1545,7 +1754,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1559,7 +1768,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1573,7 +1782,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1587,7 +1796,7 @@
     </row>
     <row r="24" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -1601,7 +1810,7 @@
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1613,80 +1822,143 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="11" t="str">
-        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="B","Riktig","Prøv igjen"))</f>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+    </row>
+    <row r="28" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="11" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="B","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
+    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-    </row>
-    <row r="32" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+    </row>
+    <row r="33" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
+    </row>
+    <row r="40" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1707,11 +1979,16 @@
     <mergeCell ref="A23:E23"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:G30"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1728,7 +2005,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1739,7 +2016,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1749,7 +2026,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1760,7 +2037,7 @@
     </row>
     <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1784,10 +2061,10 @@
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1797,10 +2074,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1810,10 +2087,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1823,10 +2100,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1836,10 +2113,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1849,10 +2126,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1862,10 +2139,10 @@
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1890,7 +2167,7 @@
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -1902,37 +2179,22 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11" t="str">
-        <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1944,66 +2206,144 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="11" t="str">
+        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="11" t="str">
+        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-    </row>
-    <row r="26" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
+      <c r="G30" s="16"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C31" s="18"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="34" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="24">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2016,13 +2356,18 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:G24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:G26"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="B31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:G35"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2039,7 +2384,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2050,7 +2395,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2060,7 +2405,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2071,7 +2416,7 @@
     </row>
     <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2095,10 +2440,10 @@
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2108,10 +2453,10 @@
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2121,10 +2466,10 @@
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2134,10 +2479,10 @@
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2147,10 +2492,10 @@
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2160,10 +2505,10 @@
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2188,7 +2533,7 @@
     </row>
     <row r="16" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -2202,7 +2547,7 @@
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
@@ -2214,94 +2559,170 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="11" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(51.4))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-    </row>
-    <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="11" t="str">
+        <f aca="false">IF(F20="","",IF(ABS(F20-(51.4))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="23" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="7"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="11" t="str">
+        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+    </row>
+    <row r="28" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
+      <c r="G31" s="16"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>147</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+    </row>
+    <row r="33" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+    </row>
+    <row r="35" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="24">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2314,12 +2735,18 @@
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="B18:G18"/>
     <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="A25:G27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:G36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ol12/OL12_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol12/OL12_Klasseoppgaver_v5.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">A2</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro: interne rammer, målet og et KI-verktøy (Egen el-bedrift)</t>
+    <t xml:space="preserve">Fjell Elektro: interne rammer, målet og et verktøy med kunstig intelligens (Egen el-bedrift)</t>
   </si>
   <si>
     <t xml:space="preserve">B1</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">Regnearket er øvingsstøtte. Det kan ikke siteres eller vises til i besvarelser, prosjektoppgaver eller eksamen; der gjelder læreboka og oppgitte primærkilder.</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 · Fjell Elektro: interne rammer, målet og et KI-verktøy</t>
+    <t xml:space="preserve">A2 · Fjell Elektro: interne rammer, målet og et verktøy med kunstig intelligens</t>
   </si>
   <si>
     <t xml:space="preserve">Kort oppsummert: Interne arbeidsbetingelser er alle forhold internt i organisasjonen som påvirker dens muligheter til å nå sine mål (innledningen til kap. 12). Et forretningsforetak har størst mulig økonomisk fortjeneste som overordnet mål, og bare aktiviteter som bidrar til måloppnåelse bør utføres (12.1). Teknologi er verktøy og metoder i produksjonen og de administrative rutinene som støtter den. Ledelsen skal spørre om teknologien gir konkurransedyktig kvalitet, er kostnadseffektiv og er trygg for mennesker og miljø (12.3).</t>
   </si>
   <si>
-    <t xml:space="preserve">Fjell Elektro AS har vært i drift i ett år. Mona Fjell er eier, daglig leder og faglig ansvarlig (installatørprøven 2023), og skriver alle tilbudene selv. Bedriften har to montører med fagbrev, verktøy og utstyr for 300 000 kr og to servicebiler på leasing. Driftsmarginen ble 3,0 % første år. Montørene henter materiell på grossistens hentelager fire ganger i uka, 45 minutter per tur, i 46 arbeidsuker. Mona vurderer et KI-verktøy som lager utkast til tilbudstekst og FDV-dokumentasjon, for 400 kr i måneden. Gå fram slik: sorter hva som er internt, velg det overordnede målet, regn timene til materiellhenting, og vurder KI-verktøyet.</t>
+    <t xml:space="preserve">Fjell Elektro AS har vært i drift i ett år. Mona Fjell er eier, daglig leder og faglig ansvarlig (installatørprøven 2023), og skriver alle tilbudene selv. Bedriften har to montører med fagbrev, verktøy og utstyr for 300 000 kr og to servicebiler på leasing. Driftsmarginen ble 3,0 % første år. Montørene henter materiell på grossistens hentelager fire ganger i uka, 45 minutter per tur, i 46 arbeidsuker. Mona vurderer et verktøy med kunstig intelligens (KI) som lager utkast til tilbudstekst og dokumentasjon for forvaltning, drift og vedlikehold (FDV), for 400 kr i måneden. Gå fram slik: sorter hva som er internt, velg det overordnede målet, regn timene til materiellhenting, og vurder KI-verktøyet.</t>
   </si>
   <si>
     <t xml:space="preserve">Mona Fjell</t>
@@ -251,10 +251,10 @@
     <t xml:space="preserve">Bransjen mangler fagarbeidere. Landsdekkende kjeder konkurrerer i Oslo øst</t>
   </si>
   <si>
-    <t xml:space="preserve">KI-verktøyet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Utkast til tilbudstekst og FDV-dokumentasjon, 400 kr i måneden</t>
+    <t xml:space="preserve">Verktøy med kunstig intelligens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utkast til tilbudstekst og dokumentasjon for forvaltning, drift og vedlikehold, 400 kr i måneden</t>
   </si>
   <si>
     <t xml:space="preserve">a)  Sorter forholdene. Er dette en intern arbeidsbetingelse for Fjell, altså et forhold inne i bedriften som påvirker muligheten til å nå målene? Svar ja eller nei for hver.</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">d)  Mona sier: «Vi er tre elektrikere. Teknologi har vi nesten ikke.» Hva er riktig etter læreboka?   A: Riktig: teknologi er datamaskiner og automatisering   B: Feil: teknologi er verktøy og metoder i produksjonen, og de administrative rutinene som støtter den   C: Riktig: små bedrifter har ingen teknologi før de kjøper programvare   (skriv bokstaven)</t>
   </si>
   <si>
-    <t xml:space="preserve">e)  Bør Mona ta i bruk KI-verktøyet? Bruk lærebokas tre spørsmål om teknologi (kvalitet, kostnad, trygghet), og si hvor grensen går for hva verktøyet kan gjøre. To–tre setninger.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bokas tre spørsmål om teknologi: konkurransedyktig kvalitet, kostnadseffektiv, trygg for mennesker og miljø (Organisasjon og ledelse 12.3). Om KI: svar formulert som om en fagperson har skrevet dem, men generert av maskin- og programvare (12.3.1).</t>
+    <t xml:space="preserve">e)  Bør Mona ta i bruk verktøyet med kunstig intelligens? Bruk lærebokas tre spørsmål om teknologi (kvalitet, kostnad, trygghet), og si hvor grensen går for hva verktøyet kan gjøre. To–tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bokas tre spørsmål om teknologi: konkurransedyktig kvalitet, kostnadseffektiv, trygg for mennesker og miljø (Organisasjon og ledelse 12.3). Om kunstig intelligens: svar formulert som om en fagperson har skrevet dem, men generert av maskin- og programvare (12.3.1).</t>
   </si>
   <si>
     <t xml:space="preserve">Internt eller eksternt</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">Et forretningsforetak styrer etter økonomiske mål (12.1). Timene: turer i uka × 0,75 time × 46 uker.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 12, innledningen (interne arbeidsbetingelser), avsnitt 12.1 (mål), 12.3 og 12.3.1 (teknologi og kunstig intelligens) og 12.5.2 (økonomi). Materiellhentingen er fra MA08. Fjell Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 12, innledningen (interne arbeidsbetingelser), avsnitt 12.1 (mål), 12.3 og 12.3.1 (teknologi og kunstig intelligens) og 12.5.2 (økonomi). Materiellhentingen er fra Markedsføring kap. 8. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys: les organisasjonskartet, og finn hullet</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">900 timer delt på 6 måneder. Fjells timer i et halvår: 3 500 / 2 = 1 750. Andel = 900 / 1 750 × 100.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 15.8.1 (entreprenørorganisasjonen), 15.6.2 (formalisering) og 15.8.5 (prosjektoppgavens kjennetegn, prosjektorganisasjon med kontrollerende autoritet), kap. 12.4 (formelle trekk) og 12.5.2 (økonomi). Haugerud-jobben er fra MA05 og MA08. Fjell Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 15.8.1 (entreprenørorganisasjonen), 15.6.2 (formalisering) og 15.8.5 (prosjektoppgavens kjennetegn, prosjektorganisasjon med kontrollerende autoritet), kap. 12.4 (formelle trekk) og 12.5.2 (økonomi). Haugerud-jobben er fra Markedsføring kap. 5 og 8. Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
 </sst>
 </file>
@@ -1571,7 +1571,7 @@
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
     </row>
-    <row r="5" customFormat="false" ht="93.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="108.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
         <v>62</v>
       </c>
@@ -1673,7 +1673,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
         <v>75</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
         <v>88</v>
       </c>

--- a/pensum/ol12/OL12_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol12/OL12_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="152">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 12: Organisasjonens interne rammebetingelser (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Organisasjon og ledelse kapittel 12: Organisasjonens interne rammebetingelser (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ol12/OL12_Klasseoppgaver_v5.xlsx
+++ b/pensum/ol12/OL12_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Læreboka deler deltagernes kompetanse i tre (12.2): formell kompetanse kan dokumenteres med vitnemål, fagbrev, kursbevis, sertifikater og attester. Realkompetanse er det en person faktisk kan, men ikke har papir på. Personlige egenskaper er blant annet samarbeidsevne, omstillingsevne og empati. Teknologi er verktøy og metoder i produksjonen, og også de administrative rutinene som støtter den (12.3). Leavitts diamant viser at mål, deltagere, teknologi og sosial struktur henger sammen: endres ett hjørne, må de andre følge med.</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Kari Nordlund vil innføre digital timeregistrering på mobil for alle de 14 montørene og lærlingene. I dag skriver montørene timelister for hånd, og kontoret taster dem inn på nytt: det tar 6 timer i uka i 46 arbeidsuker. Før hun bestemmer seg, går hun gjennom folkene. Tom Berg har fagbrev og kurs i internkontroll, kursbeviset på gjeldende norm er fra 2015, og han har tjue år med feilsøking. Ronny Fjeld har fagbrev, tolv år som leder på bygg, ingen dokumentert lederopplæring, og er direkte og god med lærlinger. Lærlingen Sara Lien har vitnemål fra Vg2 og lærekontrakt. Gå fram slik: sorter kompetansen, plasser timelistene i diamanten, regn timene, og vurder hva som må til for at Karis plan skal virke.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Kari Nordlund vil innføre digital timeregistrering på mobil for alle de 12 montørene og 2 lærlingene. I dag skriver montørene timelister for hånd, og kontoret taster dem inn på nytt: det tar 6 timer i uka i 46 arbeidsuker. Før hun bestemmer seg, går hun gjennom folkene. Tom Berg har fagbrev og kurs i internkontroll, kursbeviset på gjeldende norm er fra 2015, og han har tjue år med feilsøking. Ronny Fjeld har fagbrev, tolv år som leder på bygg, ingen dokumentert lederopplæring, og er direkte og god med lærlinger. Lærlingen Sara Lien har vitnemål fra Vg2 og lærekontrakt. Gå fram slik: sorter kompetansen, plasser timelistene i diamanten, regn timene, og vurder hva som må til for at Karis plan skal virke.</t>
   </si>
   <si>
     <t xml:space="preserve">Forutsetning</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">Karis plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Digital timeregistrering på mobil for alle 14 montører og lærlinger</t>
+    <t xml:space="preserve">Digital timeregistrering på mobil for alle 12 montører og 2 lærlinger</t>
   </si>
   <si>
     <t xml:space="preserve">Deloppgave</t>
